--- a/data/daily/2026-10/2026-10-15.xlsx
+++ b/data/daily/2026-10/2026-10-15.xlsx
@@ -1195,14 +1195,139 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1342,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,160 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
+      <row>10</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>10</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1450,207 +1450,207 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
     <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,23 +2596,11 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16275</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>피로 회복 체감 — 피곤할 때 섭취 시 활력과 힘이 나는 느낌을 줌</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>선물 만족도 높음 — 생일이나 환절기 건강 챙기기용 선물로 받거나 주기에 적합함</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>간편한 복용 방식 — 액상과 정제 구성으로 힘들 때 간편하게 섭취 가능함</t>
-        </is>
-      </c>
+        <v>16276</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -2655,23 +2643,11 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15614</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>피로 완화 효과 — 피로에 지쳤을 때 섭취 후 피로감이 덜하고 기력이 생김</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>간편한 복용법 — 복용법이 간편하여 꾸준히 챙겨 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>부담 없는 맛 — 맛이 좋아 거부감 없이 섭취 가능함</t>
-        </is>
-      </c>
+        <v>15615</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -2714,28 +2690,12 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3404</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>피로 개선 및 활력 — 복용 후 몸의 활력이 생기며 다음 날 덜 피곤한 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>진한 액상 제형 — 다른 액상 제품에 비해 진한 농도감을 지님</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>꼼꼼한 포장 배송 — 포장이 꼼꼼하게 배송되어 선물용이나 수령 시 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>아쉬운 액상 맛 — 액상 비타민 특유의 맛 자체는 아쉽다는 반응이 있음</t>
-        </is>
-      </c>
+        <v>3405</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -2779,26 +2739,10 @@
       <c r="J5" t="n">
         <v>6517</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 제형으로 간식처럼 맛있게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>간편한 복용 편의 — 알약 넘기기 힘든 사람도 부담 없이 씹어먹기 편함</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>선물용 패키지 만족 — 선물 포장이 예쁘게 구성되어 가볍게 선물하기에 좋음</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>섭취량 제한의 아쉬움 — 맛이 좋아 더 먹고 싶으나 하루 정해진 양만 먹어야 하는 아쉬움이 있음</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
@@ -2842,21 +2786,9 @@
       <c r="J6" t="n">
         <v>819</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>예쁜 선물 포장 — 기프트 에디션 포장이 예뻐서 선물용으로 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>피로 및 컨디션 관리 — 환절기 컨디션 관리와 피로 완화에 도움을 줌</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>휴대 및 섭취 간편 — 한 병씩 구성되어 출근 시 챙겨 나가 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -2901,21 +2833,9 @@
       <c r="J7" t="n">
         <v>827</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>체감 피로 완화 — 섭취 후 오후 시간대 눈의 피로나 체력 저하가 줄어들고 에너지가 충전됨</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>편리한 휴대성 — 개별 포장이 견고하여 가방에 넣어 다니며 물 없이 간편하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>올인원 영양 보충 — 하루 한 병으로 다양한 비타민과 미네랄을 한 번에 알차게 챙길 수 있음</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -2923,7 +2843,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2931,50 +2851,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>오쏘몰</t>
+          <t>정관장</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>59,800원</t>
+          <t>33,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/8167919</t>
+          <t>https://gift.kakao.com/product/12159594</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261008180237_441cb42108de40bb9ca4f55e8f361c4c.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>783</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>남녀 맞춤 구성 — 남성과 여성을 위한 비타민이 각각 구분되어 있어 선택이 용이함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>부담 없는 맛 — 비타민 특유의 쓴맛이 없어 먹기에 편안함</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>간편한 휴대 복용 — 휴대하기 편하고 한 번에 마시기 쉬워 직장인에게 적합함</t>
-        </is>
-      </c>
+        <v>1766</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -2982,7 +2890,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2990,55 +2898,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+          <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>정관장</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>33,000원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/12159594</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260812135521_25667cc1efc34a698d1813fe75189344.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261008180237_441cb42108de40bb9ca4f55e8f361c4c.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1764</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>신선한 혼합 방식 — 캡을 눌러 분말과 액체를 즉석에서 혼합해 먹는 방식이 신선함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>빠른 기력 회복 — 섭취 후 피로가 덜하고 활력 충전 효과를 체감함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>호불호 적은 맛 — 거부감 없는 맛으로 음료처럼 마시기 편함</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>목넘김 뻑뻑함 — 음용 후 목이 메여 추가로 물을 마셔야 하는 경우가 있음</t>
-        </is>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -3082,21 +2974,9 @@
       <c r="J10" t="n">
         <v>8751</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>개별 포장 및 휴대성 — 한 포씩 간편하게 챙길 수 있어 외출 시 가방에 휴대하기 편리함</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>컨디션 회복 도움 — 섭취 후 다음 날 피로 회복과 활력 개선에 도움을 체감함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>부담 없는 맛 — 맛이 강하거나 부담스럽지 않아 꾸준히 복용하기 용이함</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
@@ -3141,26 +3021,10 @@
       <c r="J11" t="n">
         <v>958</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>피로 완화 도움 — 복용 후 하루가 덜 피곤한 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>고함량 가루 제형 — 분말 형태의 고용량 비타민C로 섭취하기에 좋음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>선물 적합성 — 호불호가 적고 건강을 챙겨주는 의미의 선물로 알맞음</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>강한 신맛 — 분말 제형의 신맛이 매우 강해 섭취 시 셔하는 반응이 있음</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3202,23 +3066,11 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>1715</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>구수하고 고소한 맛 — 고소한 맛 덕분에 거부감 없이 맛있게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>장 상태 변화 체감 — 지속 섭취 시 장 상태 개선을 기대하거나 경험함</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>배려 깊은 포장 — 박스 테이프 제거 시 사람을 배려한 세심한 포장이 만족스러움</t>
-        </is>
-      </c>
+        <v>1716</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -3263,26 +3115,10 @@
       <c r="J13" t="n">
         <v>909</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>속 편안함 및 소화 — 복용 후 더부룩함이 줄고 소화가 편안해지며 몸이 가벼워짐</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>달콤한 옥수수맛 — 초당 옥수수 콘스프 느낌의 달달하고 맛있는 풍미를 지님</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>가성비 우수 — 대용량 구성 및 서비스 증정 대비 가격이 합리적임</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>맛의 편차 존재 — 이전 구매분에 비해 맛이 달라졌다는 후기가 있음</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
     </row>
@@ -3324,23 +3160,11 @@
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>256</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>맛있는 분말 효소 — 상큼하면서도 고소하여 물 없이 녹여 먹기에도 괜찮음</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>아이돌 굿즈 만족도 — 동봉된 엽서 카드와 포토카드의 퀄리티가 뛰어나 팬층 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>깔끔한 패키징 — 포장이 깔끔하고 증정 구성이 푸짐함</t>
-        </is>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
@@ -3385,21 +3209,9 @@
       <c r="J15" t="n">
         <v>68</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>촉촉한 식감과 맛 — 닭가슴살 특유의 퍽퍽함 없이 촉촉하며 잡내가 없음</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>다양한 맛 구성 — 떡볶이맛 등 다채로운 맛으로 질리지 않고 반찬처럼 식단 관리가 가능함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>간편한 조리 — 전자레인지로 간단히 데워 식사 대용으로 먹기 편리함</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -3407,7 +3219,7 @@
     <row r="16" ht="38" customHeight="1">
       <c r="B16" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3415,62 +3227,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
+          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>아일로</t>
+          <t>크런틴</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65,900원</t>
+          <t>58,200원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/4965835</t>
+          <t>https://gift.kakao.com/product/14408269</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20261014163835_db2fb775478047e286699c91aca83ed4.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>755</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 포장 — 오간자 및 플리츠백 패키지가 고급스럽고 예뻐 선물 수령 시 감동을 줌</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>피로 완화 및 피부 기대 — 피로감이 덜해지고 피부 탄력 개선에 대한 기대감이 높음</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>간편하고 좋은 맛 — 맛이 좋아 하루 한 병씩 꾸준히 마시기 편함</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 품질과 효과는 좋으나 정가 기준 가격대가 비싸게 느껴짐</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3478,50 +3274,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
+          <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>크런틴</t>
+          <t>아일로</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>58,200원</t>
+          <t>65,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14408269</t>
+          <t>https://gift.kakao.com/product/4965835</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20261014163835_db2fb775478047e286699c91aca83ed4.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260928091559_44d67bbfbab644e3bc688b7716d83f5d.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>풍부한 크런치 토핑 — 토핑과 크런치볼이 가득 씹혀 식감이 뛰어나고 포만감이 오래 지속됨</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>텁텁함 없는 단맛 — 특유의 비린맛이나 텁텁함 없이 시리얼, 쿠키맛 등 디저트처럼 맛있음</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>간편한 파우치 형태 — 파우치에 물이나 우유만 부어 흔들어 마신 뒤 바로 버릴 수 있어 편리함</t>
-        </is>
-      </c>
+        <v>755</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
@@ -3564,23 +3348,11 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>38</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>확실한 숙취 해소 — 음주 전후 섭취 시 다음 날 아침 두통과 속 울렁거림 없이 머리가 개운함</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>짜먹는 스틱 휴대성 — 개별 스틱 파우치로 가방에 넣고 다니며 물 없이 바로 짜먹기 편함</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>달콤하고 부드러운 맛 — 역한 맛 없이 벌꿀의 달달한 풍미가 있어 거부감 없이 복용 가능함</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -3625,31 +3397,11 @@
       <c r="J19" t="n">
         <v>155</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>든든한 한 끼 포만감 — 하나만 먹어도 포만감이 오래 지속되어 다이어트 식단으로 적합함</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>뛰어난 맛과 다양성 — 닭가슴살 느낌 없이 카레, 떡볶이 등 소스 맛이 훌륭함</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>증정 보냉백 만족 — 사은품으로 제공된 가방 디자인이 예쁘고 실용적임</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>일부 제품 간이 강함 — 단독으로 먹기에는 소스 간이 다소 세서 밥과 함께 먹어야 함</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>포장 터짐 및 오배송 — 진공포장 불량으로 내용물이 터져 소스가 묻거나 구성 수량이 잘못 배송됨</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
@@ -3690,23 +3442,11 @@
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>1928</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>운동 수행능력 향상 — 근력과 운동 기량 향상에 도움이 되며 꾸준히 섭취하기 좋음</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>깔끔한 성분과 스푼 — 타사 대비 성분이 깔끔하고 5g 정량 스푼이 들어있어 편리함</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>거부감 없는 섭취감 — 다른 보충제에 비해 목넘김 거부감이 적어 먹기 수월함</t>
-        </is>
-      </c>
+        <v>1930</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
@@ -3751,21 +3491,9 @@
       <c r="J21" t="n">
         <v>218</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>텁텁함 없는 깔끔한 맛 — 프로틴 특유의 비리고 텁텁한 맛 없이 달달한 음료처럼 맛있음</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>운동 후 단백질 보충 — 운동 후 한 팩 마시기 좋고 배가 든든하여 간식 대용으로 적합함</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>간편한 팩 음료 — 빨대 꽂아 간편하게 마실 수 있어 하루 하나씩 챙겨 먹기 편함</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
@@ -3911,12 +3639,12 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>홍삼/인삼</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
@@ -3968,12 +3696,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>정관장</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>오쏘몰</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>정관장</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -4025,12 +3753,12 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>'1입 증정' 오쏘몰 바이탈 m/f 남성/여성 선택가능 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -4088,13 +3816,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16275</v>
+        <v>16276</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15614</v>
+        <v>15615</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3404</v>
+        <v>3405</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>6517</v>
@@ -4106,10 +3834,10 @@
         <v>827</v>
       </c>
       <c r="I7" s="3" t="n">
+        <v>1766</v>
+      </c>
+      <c r="J7" s="3" t="n">
         <v>783</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>1764</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>8751</v>
@@ -4118,82 +3846,22 @@
         <v>958</v>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1">
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>피로 회복 체감 — 피곤할 때 섭취 시 활력과 힘이 나는 느낌을 줌
-선물 만족도 높음 — 생일이나 환절기 건강 챙기기용 선물로 받거나 주기에 적합함
-간편한 복용 방식 — 액상과 정제 구성으로 힘들 때 간편하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>피로 완화 효과 — 피로에 지쳤을 때 섭취 후 피로감이 덜하고 기력이 생김
-간편한 복용법 — 복용법이 간편하여 꾸준히 챙겨 먹기 수월함
-부담 없는 맛 — 맛이 좋아 거부감 없이 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>피로 개선 및 활력 — 복용 후 몸의 활력이 생기며 다음 날 덜 피곤한 느낌을 받음
-진한 액상 제형 — 다른 액상 제품에 비해 진한 농도감을 지님
-꼼꼼한 포장 배송 — 포장이 꼼꼼하게 배송되어 선물용이나 수령 시 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 젤리 형태 — 새콤달콤하고 쫀득한 젤리 제형으로 간식처럼 맛있게 섭취 가능함
-간편한 복용 편의 — 알약 넘기기 힘든 사람도 부담 없이 씹어먹기 편함
-선물용 패키지 만족 — 선물 포장이 예쁘게 구성되어 가볍게 선물하기에 좋음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>예쁜 선물 포장 — 기프트 에디션 포장이 예뻐서 선물용으로 만족도가 높음
-피로 및 컨디션 관리 — 환절기 컨디션 관리와 피로 완화에 도움을 줌
-휴대 및 섭취 간편 — 한 병씩 구성되어 출근 시 챙겨 나가 부담 없이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>체감 피로 완화 — 섭취 후 오후 시간대 눈의 피로나 체력 저하가 줄어들고 에너지가 충전됨
-편리한 휴대성 — 개별 포장이 견고하여 가방에 넣어 다니며 물 없이 간편하게 섭취 가능함
-올인원 영양 보충 — 하루 한 병으로 다양한 비타민과 미네랄을 한 번에 알차게 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>남녀 맞춤 구성 — 남성과 여성을 위한 비타민이 각각 구분되어 있어 선택이 용이함
-부담 없는 맛 — 비타민 특유의 쓴맛이 없어 먹기에 편안함
-간편한 휴대 복용 — 휴대하기 편하고 한 번에 마시기 쉬워 직장인에게 적합함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>신선한 혼합 방식 — 캡을 눌러 분말과 액체를 즉석에서 혼합해 먹는 방식이 신선함
-빠른 기력 회복 — 섭취 후 피로가 덜하고 활력 충전 효과를 체감함
-호불호 적은 맛 — 거부감 없는 맛으로 음료처럼 마시기 편함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>개별 포장 및 휴대성 — 한 포씩 간편하게 챙길 수 있어 외출 시 가방에 휴대하기 편리함
-컨디션 회복 도움 — 섭취 후 다음 날 피로 회복과 활력 개선에 도움을 체감함
-부담 없는 맛 — 맛이 강하거나 부담스럽지 않아 꾸준히 복용하기 용이함</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>피로 완화 도움 — 복용 후 하루가 덜 피곤한 느낌을 받음
-고함량 가루 제형 — 분말 형태의 고용량 비타민C로 섭취하기에 좋음
-선물 적합성 — 호불호가 적고 건강을 챙겨주는 의미의 선물로 알맞음</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -4203,30 +3871,14 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>아쉬운 액상 맛 — 액상 비타민 특유의 맛 자체는 아쉽다는 반응이 있음</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>섭취량 제한의 아쉬움 — 맛이 좋아 더 먹고 싶으나 하루 정해진 양만 먹어야 하는 아쉬움이 있음</t>
-        </is>
-      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>목넘김 뻑뻑함 — 음용 후 목이 메여 추가로 물을 마셔야 하는 경우가 있음</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>강한 신맛 — 분말 제형의 신맛이 매우 강해 섭취 시 셔하는 반응이 있음</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4266,12 +3918,12 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
+          <t>33,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
           <t>59,800원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>33,000원</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -4444,12 +4096,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -4501,12 +4153,12 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
+          <t>크런틴</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
           <t>아일로</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>크런틴</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
@@ -4558,12 +4210,12 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
+          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
           <t>"선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 2입 추가 증정</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>[골라담기] 식단관리 크런틴 크런치볼 단백질쉐이크 2박스 50g x 10포</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -4631,140 +4283,67 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>909</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F19" s="3" t="n">
         <v>68</v>
       </c>
       <c r="G19" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="3" t="n">
         <v>755</v>
       </c>
-      <c r="H19" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="I19" s="3" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>155</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>218</v>
       </c>
     </row>
-    <row r="20" ht="90" customHeight="1">
+    <row r="20">
       <c r="B20" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>구수하고 고소한 맛 — 고소한 맛 덕분에 거부감 없이 맛있게 섭취 가능함
-장 상태 변화 체감 — 지속 섭취 시 장 상태 개선을 기대하거나 경험함
-배려 깊은 포장 — 박스 테이프 제거 시 사람을 배려한 세심한 포장이 만족스러움</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>속 편안함 및 소화 — 복용 후 더부룩함이 줄고 소화가 편안해지며 몸이 가벼워짐
-달콤한 옥수수맛 — 초당 옥수수 콘스프 느낌의 달달하고 맛있는 풍미를 지님
-가성비 우수 — 대용량 구성 및 서비스 증정 대비 가격이 합리적임</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 분말 효소 — 상큼하면서도 고소하여 물 없이 녹여 먹기에도 괜찮음
-아이돌 굿즈 만족도 — 동봉된 엽서 카드와 포토카드의 퀄리티가 뛰어나 팬층 만족도가 높음
-깔끔한 패키징 — 포장이 깔끔하고 증정 구성이 푸짐함</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>촉촉한 식감과 맛 — 닭가슴살 특유의 퍽퍽함 없이 촉촉하며 잡내가 없음
-다양한 맛 구성 — 떡볶이맛 등 다채로운 맛으로 질리지 않고 반찬처럼 식단 관리가 가능함
-간편한 조리 — 전자레인지로 간단히 데워 식사 대용으로 먹기 편리함</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>고급스러운 선물 포장 — 오간자 및 플리츠백 패키지가 고급스럽고 예뻐 선물 수령 시 감동을 줌
-피로 완화 및 피부 기대 — 피로감이 덜해지고 피부 탄력 개선에 대한 기대감이 높음
-간편하고 좋은 맛 — 맛이 좋아 하루 한 병씩 꾸준히 마시기 편함</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>풍부한 크런치 토핑 — 토핑과 크런치볼이 가득 씹혀 식감이 뛰어나고 포만감이 오래 지속됨
-텁텁함 없는 단맛 — 특유의 비린맛이나 텁텁함 없이 시리얼, 쿠키맛 등 디저트처럼 맛있음
-간편한 파우치 형태 — 파우치에 물이나 우유만 부어 흔들어 마신 뒤 바로 버릴 수 있어 편리함</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>확실한 숙취 해소 — 음주 전후 섭취 시 다음 날 아침 두통과 속 울렁거림 없이 머리가 개운함
-짜먹는 스틱 휴대성 — 개별 스틱 파우치로 가방에 넣고 다니며 물 없이 바로 짜먹기 편함
-달콤하고 부드러운 맛 — 역한 맛 없이 벌꿀의 달달한 풍미가 있어 거부감 없이 복용 가능함</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>든든한 한 끼 포만감 — 하나만 먹어도 포만감이 오래 지속되어 다이어트 식단으로 적합함
-뛰어난 맛과 다양성 — 닭가슴살 느낌 없이 카레, 떡볶이 등 소스 맛이 훌륭함
-증정 보냉백 만족 — 사은품으로 제공된 가방 디자인이 예쁘고 실용적임</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>운동 수행능력 향상 — 근력과 운동 기량 향상에 도움이 되며 꾸준히 섭취하기 좋음
-깔끔한 성분과 스푼 — 타사 대비 성분이 깔끔하고 5g 정량 스푼이 들어있어 편리함
-거부감 없는 섭취감 — 다른 보충제에 비해 목넘김 거부감이 적어 먹기 수월함</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>텁텁함 없는 깔끔한 맛 — 프로틴 특유의 비리고 텁텁한 맛 없이 달달한 음료처럼 맛있음
-운동 후 단백질 보충 — 운동 후 한 팩 마시기 좋고 배가 든든하여 간식 대용으로 적합함
-간편한 팩 음료 — 빨대 꽂아 간편하게 마실 수 있어 하루 하나씩 챙겨 먹기 편함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+      <c r="J20" s="3" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr"/>
+      <c r="L20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>맛의 편차 존재 — 이전 구매분에 비해 맛이 달라졌다는 후기가 있음</t>
-        </is>
-      </c>
+      <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>다소 높은 가격대 — 품질과 효과는 좋으나 정가 기준 가격대가 비싸게 느껴짐</t>
-        </is>
-      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>일부 제품 간이 강함 — 단독으로 먹기에는 소스 간이 다소 세서 밥과 함께 먹어야 함
-포장 터짐 및 오배송 — 진공포장 불량으로 내용물이 터져 소스가 묻거나 구성 수량이 잘못 배송됨</t>
-        </is>
-      </c>
+      <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
@@ -4796,12 +4375,12 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>58,200원</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>65,900원</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>58,200원</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
@@ -5011,7 +4590,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5019,50 +4598,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 아르기닌 5포 5일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618639&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260703/B8ckjHxaPLARUlbtHVdP601618639_00_02B8ckjHxaPLARUlbtHVdP.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>586</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>간편한 액상 섭취 — 액상 제형이라 먹기 편하고 맛이 좋아 마시기 수월함</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>즉각적인 활력 체감 — 마신 뒤 빠르게 기운과 활력이 나는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>가격 대비 만족도 — 부담 없는 가격에 마그네슘과 아르기닌을 보충하기에 적합함</t>
-        </is>
-      </c>
+        <v>3692</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -5070,7 +4637,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5078,58 +4645,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911029&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260623/QaObI3LjZ86tREQcCYCw610911029_00_00QaObI3LjZ86tREQcCYCw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>560</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>배변 활동 도움 — 만성 변비 탈출 등 장을 비워내는 배변 효과가 뛰어남</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>높은 접근성 — 다이소 매장에서 손쉽게 발견하여 구매하기 편리함</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>복통 가능성 — 섭취 후 장 반응으로 인해 배가 아프다는 후기가 있음</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5137,51 +4692,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000278&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/uooE7Z5tFnMjhhremBna600000278_00_01uooE7Z5tFnMjhhremBna.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1164</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>간편한 아침 섭취 — 바쁜 아침 시간에 간편하고 깔끔하게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>배변 원활 도움 — 물에 타서 꾸준히 음용 시 아침 화장실 가기가 수월해짐</t>
-        </is>
-      </c>
+        <v>840</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>강한 레몬 신맛 — 레몬 특유의 신맛이 다소 강하게 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -5196,7 +4739,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>대웅제약 MSM 90정 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5211,43 +4754,31 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000134&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000149&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/bzKNvkJzwy2KdAqrXtDQ600000134_00_00bzKNvkJzwy2KdAqrXtDQ.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/gVoECGdnaBQU8HtRPGFz600000149_00_00gVoECGdnaBQU8HtRPGFz.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4079</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>높은 가성비 — 저렴한 가격으로 간 건강을 챙길 수 있어 가격 대비 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>간편한 복용 — 알약 형태로 되어 있어 매일 꾸준히 섭취하기에 부담이 없음</t>
-        </is>
-      </c>
+        <v>1056</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>체감 효과 미미 — 꾸준히 먹고 있으나 즉각적인 신체 효과는 잘 모르겠다는 의견이 있음</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5255,7 +4786,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5265,40 +4796,28 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000128&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/DZz3h5SxY2J2FqaEB9qZ600000128_00_00DZz3h5SxY2J2FqaEB9qZ.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>350</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>소용량 체험 구매 — 10일분 소분 포장으로 몸에 맞는지 부담 없이 테스트해보기 좋음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>뛰어난 가성비 — 저렴한 가격으로 고함량 비타민D를 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>높은 구매 접근성 — 다이소에서 간편하게 구할 수 있어 구매가 용이함</t>
-        </is>
-      </c>
+        <v>6894</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -5306,7 +4825,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5314,58 +4833,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000142&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618636&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/CJUce0AJqtqHn7R3ZFm1600000142_00_00CJUce0AJqtqHn7R3ZFm1.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260414/Rr7eEkWvVmX4lCcRcfuW601618636_00_00Rr7eEkWvVmX4lCcRcfuW.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>640</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>아이들의 높은 선호도 — 맛있는 츄어블 형태라 아이들이 거부감 없이 스스로 잘 씹어 먹음</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>성인 겸용 가성비 — 온 가족이 함께 먹기 좋고 가격 대비 구성이 만족스러움</t>
-        </is>
-      </c>
+        <v>3656</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>섭취 후 양치 필요 — 츄어블 특성상 치아에 남아 양치가 필요해 물로 넘기는 경우가 있음</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5373,58 +4880,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>[의약외품][신혜선 PICK] 동국 벤포 비타맥스정 10정 10일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000203&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911056&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251202/7FdyxsWTlcbRJnDROGoC600000203_00_007FdyxsWTlcbRJnDROGoC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260710/5mTQPvsktLduwds14llY610911056_00_005mTQPvsktLduwds14llY.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1740</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>어취 없는 레몬향 — 식물성 원료라 비린내가 안 나고 은은한 레몬 향이 나서 먹기 편함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>우수한 가성비 — 저렴한 가격에 부담 없이 한 달치 섭취가 가능함</t>
-        </is>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>알약 크기 부담 — 알약 사이즈가 다소 커서 삼킬 때 목넘김이 불편할 수 있음</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5432,12 +4927,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5447,43 +4942,31 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911092&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260814/qU3FUPerTqzVYxrqf7Lx610911092_00_01qU3FUPerTqzVYxrqf7Lx.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>189</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>고함량 대비 저렴 — 비타민C 2000mg 고용량 분말을 가성비 있게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>메가도스용 적합 — 고용량 비타민이라 메가도스 용도로 온 가족이 먹기 좋음</t>
-        </is>
-      </c>
+        <v>6734</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>지나치게 쓴맛과 신맛 — 신맛이 지나치게 강하고 끝맛이 써서 물 없이 그냥 넘기기 힘듦</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5491,12 +4974,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>유한양행 초코맛 생유산균 스틱 20포 20일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>유한양행</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5506,43 +4989,31 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651652&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260325/dj7lmBMZiAKAXlm5drGt600651652_00_00dj7lmBMZiAKAXlm5drGt.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>482</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>간식 같은 초코맛 — 초코맛이라 아이들이 좋아하며 간식처럼 맛있게 먹음</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>배변 활동 원활 — 하루 한 포 섭취 시 화장실을 잘 가게 됨</t>
-        </is>
-      </c>
+        <v>2865</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>다소 묘한 초코맛 — 생각보다 맛이 낯설거나 유산균 느낌이 덜 든다는 의견이 있음</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5550,51 +5021,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>2905</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>저렴한 가성비 — 가격이 매우 저렴하여 부담 없이 꾸준히 구매하기 좋음</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>간편한 알약 제형 — 물과 함께 삼키는 정제 타입이라 분말보다 먹기 편함</t>
-        </is>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>뚜렷한 체감 부족 — 신체적인 직접 효과보다는 심리적인 만족감으로 섭취함</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5709,52 +5168,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>마그네슘</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -5766,52 +5225,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>동화약품</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>자연관</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>유한양행</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
         </is>
       </c>
     </row>
@@ -5823,52 +5282,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘 아르기닌 5포 5일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국 마이팝 푸룬＆식이섬유</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>대웅제약 바나바잎 10정 10일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 밀크씨슬 30정 30일분</t>
+          <t>대웅제약 MSM 90정 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
+          <t>대웅제약 마그네슘 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 츄어블 60정 30일분</t>
+          <t>동화 부채표 편안활 5포 5일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 식물성 뉴티지 오메가3 30캡슐 30일분</t>
+          <t>[의약외품][신혜선 PICK] 동국 벤포 비타맥스정 10정 10일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>유한양행 초코맛 생유산균 스틱 20포 20일분</t>
+          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
     </row>
@@ -5882,7 +5341,7 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
@@ -5897,16 +5356,16 @@
         <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="K6" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="7">
@@ -5916,104 +5375,52 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>586</v>
+        <v>3692</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>560</v>
+        <v>350</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1164</v>
+        <v>840</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4079</v>
+        <v>1056</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>350</v>
+        <v>6894</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>640</v>
+        <v>3656</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>1740</v>
+        <v>139</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>189</v>
+        <v>6734</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>482</v>
+        <v>2865</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2905</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>간편한 액상 섭취 — 액상 제형이라 먹기 편하고 맛이 좋아 마시기 수월함
-즉각적인 활력 체감 — 마신 뒤 빠르게 기운과 활력이 나는 느낌을 받음
-가격 대비 만족도 — 부담 없는 가격에 마그네슘과 아르기닌을 보충하기에 적합함</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>배변 활동 도움 — 만성 변비 탈출 등 장을 비워내는 배변 효과가 뛰어남
-높은 접근성 — 다이소 매장에서 손쉽게 발견하여 구매하기 편리함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>간편한 아침 섭취 — 바쁜 아침 시간에 간편하고 깔끔하게 먹기 좋음
-배변 원활 도움 — 물에 타서 꾸준히 음용 시 아침 화장실 가기가 수월해짐</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>높은 가성비 — 저렴한 가격으로 간 건강을 챙길 수 있어 가격 대비 만족도가 높음
-간편한 복용 — 알약 형태로 되어 있어 매일 꾸준히 섭취하기에 부담이 없음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>소용량 체험 구매 — 10일분 소분 포장으로 몸에 맞는지 부담 없이 테스트해보기 좋음
-뛰어난 가성비 — 저렴한 가격으로 고함량 비타민D를 챙길 수 있음
-높은 구매 접근성 — 다이소에서 간편하게 구할 수 있어 구매가 용이함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>아이들의 높은 선호도 — 맛있는 츄어블 형태라 아이들이 거부감 없이 스스로 잘 씹어 먹음
-성인 겸용 가성비 — 온 가족이 함께 먹기 좋고 가격 대비 구성이 만족스러움</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>어취 없는 레몬향 — 식물성 원료라 비린내가 안 나고 은은한 레몬 향이 나서 먹기 편함
-우수한 가성비 — 저렴한 가격에 부담 없이 한 달치 섭취가 가능함</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>고함량 대비 저렴 — 비타민C 2000mg 고용량 분말을 가성비 있게 섭취 가능함
-메가도스용 적합 — 고용량 비타민이라 메가도스 용도로 온 가족이 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>간식 같은 초코맛 — 초코맛이라 아이들이 좋아하며 간식처럼 맛있게 먹음
-배변 활동 원활 — 하루 한 포 섭취 시 화장실을 잘 가게 됨</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>저렴한 가성비 — 가격이 매우 저렴하여 부담 없이 꾸준히 구매하기 좋음
-간편한 알약 제형 — 물과 함께 삼키는 정제 타입이라 분말보다 먹기 편함</t>
-        </is>
-      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr"/>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -6022,47 +5429,15 @@
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>복통 가능성 — 섭취 후 장 반응으로 인해 배가 아프다는 후기가 있음</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>강한 레몬 신맛 — 레몬 특유의 신맛이 다소 강하게 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>체감 효과 미미 — 꾸준히 먹고 있으나 즉각적인 신체 효과는 잘 모르겠다는 의견이 있음</t>
-        </is>
-      </c>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>섭취 후 양치 필요 — 츄어블 특성상 치아에 남아 양치가 필요해 물로 넘기는 경우가 있음</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>알약 크기 부담 — 알약 사이즈가 다소 커서 삼킬 때 목넘김이 불편할 수 있음</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>지나치게 쓴맛과 신맛 — 신맛이 지나치게 강하고 끝맛이 써서 물 없이 그냥 넘기기 힘듦</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>다소 묘한 초코맛 — 생각보다 맛이 낯설거나 유산균 느낌이 덜 든다는 의견이 있음</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>뚜렷한 체감 부족 — 신체적인 직접 효과보다는 심리적인 만족감으로 섭취함</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -6072,52 +5447,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>1,000원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
     </row>
@@ -6296,7 +5671,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6304,27 +5679,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35,800원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6339,7 +5714,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6347,27 +5722,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>생활약속</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24,000원</t>
+          <t>16,200원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261662&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026166204ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -6382,7 +5757,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6390,31 +5765,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30,400원</t>
+          <t>35,800원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549621ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>614</v>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -6425,7 +5804,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6433,46 +5812,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[올영단독] 닥터린 파비플로라 알파CD 프리미엄 10g X 30포 (1개월분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>닥터린</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>17,060원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236821&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>초소형 캡슐 목넘김 — 캡슐 크기가 170mg으로 매우 작고 가벼워 물과 함께 삼키기 아주 수월함</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>질과 장 더블케어 — 식약처 인정 원료로 질과 장 건강을 한 번에 관리할 수 있음</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 증정 굿즈 만족도가 높음</t>
-        </is>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023682102ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>564</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -6488,31 +5859,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>24,000원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261662&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026166204ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -6523,7 +5898,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6531,31 +5906,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25457</v>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -6566,7 +5945,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6574,27 +5953,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>푸드올로지</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>26,800원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246272&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627206ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563488ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6617,34 +5996,34 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>딥트3일</t>
+          <t>씨제이웰케어</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11,400원</t>
+          <t>5,900원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000211396&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021139617ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024786106ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1560</v>
+        <v>20863</v>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -6656,7 +6035,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6664,34 +6043,34 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>생활약속</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>16,200원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000180121&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018012128ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>17438</v>
+        <v>8556</v>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -6703,7 +6082,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6711,34 +6090,34 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>오쏘몰 바이탈 M/F 멀티비타민&amp;미네랄 7입 (남성/여성)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246271&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000199174&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024627107ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019917425ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>284</v>
+        <v>5122</v>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
@@ -6858,52 +6237,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -6915,52 +6294,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>생활약속</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>닥터린</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>바이오코어유산균</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>푸드올로지</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>씨제이웰케어</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>글로우뮤즈</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>딥트3일</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>생활약속</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>글로우뮤즈</t>
+          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -6972,52 +6351,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>[올영단독] 닥터린 파비플로라 알파CD 프리미엄 10g X 30포 (1개월분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>CJ BYOCORE 바나나효소 30포 + 키캡 키링 (1개월분)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[골라담기] CJ웰케어 건강루틴 가격혁명 12종 택 1</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>콜레올로지 PRO 600mg*30정/60정/120정 (15/30/60일분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[피부건강] 글로우뮤즈 스킨 밸런스 파우더 레몬맛 14포 (14일분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[딥트3일/남규리PICK]남규리의 바른 효소 리셋 8포</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[곽민경 PICK] 생활약속 기분전환 알파플러스 10포 (+1포 증정기획)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>[속광콜라겐] 글로우뮤즈 올데이 글로우 콜라겐 복숭아 14포 (14일분)</t>
+          <t>오쏘몰 바이탈 M/F 멀티비타민&amp;미네랄 7입 (남성/여성)</t>
         </is>
       </c>
     </row>
@@ -7029,19 +6408,27 @@
       </c>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
-      <c r="F6" s="3" t="inlineStr"/>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.9</v>
+      </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -7052,22 +6439,30 @@
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="n">
+        <v>614</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>564</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>25457</v>
+      </c>
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="n">
-        <v>1560</v>
+        <v>20863</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>17438</v>
+        <v>8556</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>5122</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -7076,13 +6471,7 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
       <c r="E8" s="3" t="inlineStr"/>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>초소형 캡슐 목넘김 — 캡슐 크기가 170mg으로 매우 작고 가벼워 물과 함께 삼키기 아주 수월함
-질과 장 더블케어 — 식약처 인정 원료로 질과 장 건강을 한 번에 관리할 수 있음
-귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 증정 굿즈 만족도가 높음</t>
-        </is>
-      </c>
+      <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr"/>
       <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
@@ -7115,52 +6504,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>16,200원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>35,800원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>17,060원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>24,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>30,400원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>17,900원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>5,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>31,400원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>17,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>26,800원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>11,400원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>16,200원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>31,900원</t>
         </is>
       </c>
     </row>
@@ -7290,25 +6679,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>32.5</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
-      </c>
-      <c r="F2" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7318,35 +6707,35 @@
         <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20</v>
+      </c>
+      <c r="D4" t="n">
         <v>7</v>
-      </c>
-      <c r="C4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7356,16 +6745,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -7374,17 +6763,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
@@ -7396,14 +6785,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -7412,13 +6801,13 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7428,10 +6817,10 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7440,7 +6829,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7462,7 +6851,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7484,7 +6873,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B11" t="n">
